--- a/output/tables/table_variable_summary_XGB.xlsx
+++ b/output/tables/table_variable_summary_XGB.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Feb 1994</t>
   </si>
   <si>
-    <t xml:space="preserve">Sept 2025</t>
+    <t xml:space="preserve">Aug 2025</t>
   </si>
   <si>
     <t xml:space="preserve">Monthly</t>
@@ -325,6 +325,9 @@
     <t xml:space="preserve">sq_error</t>
   </si>
   <si>
+    <t xml:space="preserve">Mar 2016</t>
+  </si>
+  <si>
     <t xml:space="preserve">Apr 2016</t>
   </si>
   <si>
@@ -659,9 +662,6 @@
   </si>
   <si>
     <t xml:space="preserve">Jul 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aug 2025</t>
   </si>
 </sst>
 </file>
@@ -1105,7 +1105,7 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -1697,10 +1697,10 @@
         <v>20</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.103</v>
+        <v>-0.095</v>
       </c>
       <c r="C3" t="n">
-        <v>4.079</v>
+        <v>4.081</v>
       </c>
       <c r="D3" t="n">
         <v>-17.3</v>
@@ -1709,7 +1709,7 @@
         <v>11.2</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -1823,10 +1823,10 @@
         <v>0.006</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.014</v>
+        <v>-0.015</v>
       </c>
       <c r="E9" t="n">
-        <v>0.062</v>
+        <v>0.061</v>
       </c>
       <c r="F9" t="n">
         <v>0.004</v>
@@ -1857,19 +1857,19 @@
         <v>37</v>
       </c>
       <c r="B11" t="n">
-        <v>-139.961</v>
+        <v>-139.995</v>
       </c>
       <c r="C11" t="n">
-        <v>5733.056</v>
+        <v>5957.35</v>
       </c>
       <c r="D11" t="n">
-        <v>-27855</v>
+        <v>-31853</v>
       </c>
       <c r="E11" t="n">
-        <v>72642</v>
+        <v>76228</v>
       </c>
       <c r="F11" t="n">
-        <v>-252</v>
+        <v>-358</v>
       </c>
     </row>
     <row r="12">
@@ -1929,7 +1929,7 @@
         <v>0.615</v>
       </c>
       <c r="F14" t="n">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="15">
@@ -2009,7 +2009,7 @@
         <v>0.215</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.001</v>
+        <v>-0.002</v>
       </c>
     </row>
     <row r="19">
@@ -2040,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>0.376</v>
+        <v>0.377</v>
       </c>
       <c r="D20" t="n">
         <v>-1.297</v>
@@ -2049,7 +2049,7 @@
         <v>1.71</v>
       </c>
       <c r="F20" t="n">
-        <v>0.006</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="21">
@@ -2057,10 +2057,10 @@
         <v>57</v>
       </c>
       <c r="B21" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="C21" t="n">
-        <v>0.871</v>
+        <v>0.872</v>
       </c>
       <c r="D21" t="n">
         <v>-3.176</v>
@@ -2069,7 +2069,7 @@
         <v>6.858</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.049</v>
+        <v>-0.045</v>
       </c>
     </row>
     <row r="22">
@@ -2120,7 +2120,7 @@
         <v>0.002</v>
       </c>
       <c r="C24" t="n">
-        <v>0.02</v>
+        <v>0.021</v>
       </c>
       <c r="D24" t="n">
         <v>-0.063</v>
@@ -2157,19 +2157,19 @@
         <v>67</v>
       </c>
       <c r="B26" t="n">
-        <v>0.015</v>
+        <v>0.003</v>
       </c>
       <c r="C26" t="n">
-        <v>0.989</v>
+        <v>0.984</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.127</v>
+        <v>-1.134</v>
       </c>
       <c r="E26" t="n">
-        <v>7.798</v>
+        <v>7.748</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.204</v>
+        <v>-0.209</v>
       </c>
     </row>
     <row r="27">
@@ -2177,10 +2177,10 @@
         <v>70</v>
       </c>
       <c r="B27" t="n">
-        <v>2.549</v>
+        <v>2.548</v>
       </c>
       <c r="C27" t="n">
-        <v>1.586</v>
+        <v>1.588</v>
       </c>
       <c r="D27" t="n">
         <v>-1.959</v>
@@ -2189,7 +2189,7 @@
         <v>8.999</v>
       </c>
       <c r="F27" t="n">
-        <v>2.426</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="28">
@@ -2200,7 +2200,7 @@
         <v>0.006</v>
       </c>
       <c r="C28" t="n">
-        <v>0.045</v>
+        <v>0.044</v>
       </c>
       <c r="D28" t="n">
         <v>-0.208</v>
@@ -2209,7 +2209,7 @@
         <v>0.177</v>
       </c>
       <c r="F28" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="29">
@@ -2349,7 +2349,7 @@
         <v>94</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7464</v>
+        <v>0.7515</v>
       </c>
     </row>
     <row r="3">
@@ -2360,7 +2360,7 @@
         <v>49</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0552</v>
+        <v>0.068</v>
       </c>
     </row>
     <row r="4">
@@ -2371,7 +2371,7 @@
         <v>22</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0314</v>
+        <v>0.0316</v>
       </c>
     </row>
     <row r="5">
@@ -2382,7 +2382,7 @@
         <v>65</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0279</v>
+        <v>0.0282</v>
       </c>
     </row>
     <row r="6">
@@ -2393,7 +2393,7 @@
         <v>41</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0225</v>
+        <v>0.0198</v>
       </c>
     </row>
     <row r="7">
@@ -2401,10 +2401,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C7" t="n">
-        <v>0.019</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="8">
@@ -2412,10 +2412,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0164</v>
+        <v>0.0141</v>
       </c>
     </row>
     <row r="9">
@@ -2423,10 +2423,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0113</v>
+        <v>0.0133</v>
       </c>
     </row>
     <row r="10">
@@ -2434,10 +2434,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0105</v>
+        <v>0.0079</v>
       </c>
     </row>
     <row r="11">
@@ -2445,10 +2445,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0104</v>
+        <v>0.0078</v>
       </c>
     </row>
     <row r="12">
@@ -2456,10 +2456,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0085</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="13">
@@ -2467,10 +2467,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0078</v>
+        <v>0.0062</v>
       </c>
     </row>
     <row r="14">
@@ -2478,10 +2478,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0071</v>
+        <v>0.0058</v>
       </c>
     </row>
     <row r="15">
@@ -2492,7 +2492,7 @@
         <v>25</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0049</v>
+        <v>0.0047</v>
       </c>
     </row>
     <row r="16">
@@ -2503,7 +2503,7 @@
         <v>59</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0026</v>
+        <v>0.0027</v>
       </c>
     </row>
     <row r="17">
@@ -2514,7 +2514,7 @@
         <v>33</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0025</v>
+        <v>0.0023</v>
       </c>
     </row>
     <row r="18">
@@ -2533,7 +2533,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="C19" t="n">
         <v>0.0003</v>
@@ -2544,7 +2544,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C20" t="n">
         <v>0.0003</v>
@@ -2555,7 +2555,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C21" t="n">
         <v>0.0003</v>
@@ -2566,7 +2566,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="C22" t="n">
         <v>0.0003</v>
@@ -2577,7 +2577,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C23" t="n">
         <v>0.0003</v>
@@ -2588,10 +2588,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0003</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="25">
@@ -2599,7 +2599,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C25" t="n">
         <v>0.0002</v>
@@ -2610,7 +2610,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="C26" t="n">
         <v>0.0002</v>
@@ -2621,7 +2621,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C27" t="n">
         <v>0.0002</v>
@@ -2632,7 +2632,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="C28" t="n">
         <v>0.0002</v>
@@ -2643,7 +2643,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="C29" t="n">
         <v>0.0002</v>
@@ -2691,22 +2691,22 @@
         <v>102</v>
       </c>
       <c r="B2" t="n">
-        <v>1.173</v>
+        <v>0.892</v>
       </c>
       <c r="C2" t="n">
-        <v>1.234</v>
+        <v>0.769</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>42461</v>
+        <v>42430</v>
       </c>
       <c r="E2" t="n">
-        <v>0.061</v>
+        <v>-0.122</v>
       </c>
       <c r="F2" t="n">
-        <v>0.061</v>
+        <v>0.122</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0038</v>
+        <v>0.0149</v>
       </c>
     </row>
     <row r="3">
@@ -2714,22 +2714,22 @@
         <v>103</v>
       </c>
       <c r="B3" t="n">
-        <v>1.078</v>
+        <v>1.173</v>
       </c>
       <c r="C3" t="n">
-        <v>1.485</v>
+        <v>1.23</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>42491</v>
+        <v>42461</v>
       </c>
       <c r="E3" t="n">
-        <v>0.406</v>
+        <v>0.057</v>
       </c>
       <c r="F3" t="n">
-        <v>0.406</v>
+        <v>0.057</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1649</v>
+        <v>0.0032</v>
       </c>
     </row>
     <row r="4">
@@ -2737,22 +2737,22 @@
         <v>104</v>
       </c>
       <c r="B4" t="n">
-        <v>1.079</v>
+        <v>1.078</v>
       </c>
       <c r="C4" t="n">
-        <v>1.188</v>
+        <v>1.48</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>42522</v>
+        <v>42491</v>
       </c>
       <c r="E4" t="n">
-        <v>0.109</v>
+        <v>0.402</v>
       </c>
       <c r="F4" t="n">
-        <v>0.109</v>
+        <v>0.402</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0119</v>
+        <v>0.1615</v>
       </c>
     </row>
     <row r="5">
@@ -2760,22 +2760,22 @@
         <v>105</v>
       </c>
       <c r="B5" t="n">
-        <v>0.868</v>
+        <v>1.079</v>
       </c>
       <c r="C5" t="n">
-        <v>1.189</v>
+        <v>1.208</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>42552</v>
+        <v>42522</v>
       </c>
       <c r="E5" t="n">
-        <v>0.32</v>
+        <v>0.129</v>
       </c>
       <c r="F5" t="n">
-        <v>0.32</v>
+        <v>0.129</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1026</v>
+        <v>0.0166</v>
       </c>
     </row>
     <row r="6">
@@ -2783,22 +2783,22 @@
         <v>106</v>
       </c>
       <c r="B6" t="n">
-        <v>1.055</v>
+        <v>0.868</v>
       </c>
       <c r="C6" t="n">
-        <v>0.978</v>
+        <v>1.18</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>42583</v>
+        <v>42552</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.078</v>
+        <v>0.312</v>
       </c>
       <c r="F6" t="n">
-        <v>0.078</v>
+        <v>0.312</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006</v>
+        <v>0.0974</v>
       </c>
     </row>
     <row r="7">
@@ -2806,22 +2806,22 @@
         <v>107</v>
       </c>
       <c r="B7" t="n">
-        <v>1.549</v>
+        <v>1.055</v>
       </c>
       <c r="C7" t="n">
-        <v>1.12</v>
+        <v>0.673</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>42614</v>
+        <v>42583</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.429</v>
+        <v>-0.383</v>
       </c>
       <c r="F7" t="n">
-        <v>0.429</v>
+        <v>0.383</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1837</v>
+        <v>0.1464</v>
       </c>
     </row>
     <row r="8">
@@ -2829,22 +2829,22 @@
         <v>108</v>
       </c>
       <c r="B8" t="n">
-        <v>1.686</v>
+        <v>1.549</v>
       </c>
       <c r="C8" t="n">
-        <v>1.598</v>
+        <v>1.109</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>42644</v>
+        <v>42614</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.087</v>
+        <v>-0.44</v>
       </c>
       <c r="F8" t="n">
-        <v>0.087</v>
+        <v>0.44</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0076</v>
+        <v>0.1933</v>
       </c>
     </row>
     <row r="9">
@@ -2852,22 +2852,22 @@
         <v>109</v>
       </c>
       <c r="B9" t="n">
-        <v>1.684</v>
+        <v>1.686</v>
       </c>
       <c r="C9" t="n">
-        <v>1.771</v>
+        <v>1.625</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>42675</v>
+        <v>42644</v>
       </c>
       <c r="E9" t="n">
-        <v>0.087</v>
+        <v>-0.061</v>
       </c>
       <c r="F9" t="n">
-        <v>0.087</v>
+        <v>0.061</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0076</v>
+        <v>0.0038</v>
       </c>
     </row>
     <row r="10">
@@ -2875,22 +2875,22 @@
         <v>110</v>
       </c>
       <c r="B10" t="n">
-        <v>2.051</v>
+        <v>1.684</v>
       </c>
       <c r="C10" t="n">
-        <v>1.924</v>
+        <v>1.793</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>42705</v>
+        <v>42675</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.127</v>
+        <v>0.109</v>
       </c>
       <c r="F10" t="n">
-        <v>0.127</v>
+        <v>0.109</v>
       </c>
       <c r="G10" t="n">
-        <v>0.016</v>
+        <v>0.0118</v>
       </c>
     </row>
     <row r="11">
@@ -2898,22 +2898,22 @@
         <v>111</v>
       </c>
       <c r="B11" t="n">
-        <v>2.51</v>
+        <v>2.051</v>
       </c>
       <c r="C11" t="n">
-        <v>2.213</v>
+        <v>1.947</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>42736</v>
+        <v>42705</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.298</v>
+        <v>-0.103</v>
       </c>
       <c r="F11" t="n">
-        <v>0.298</v>
+        <v>0.103</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0885</v>
+        <v>0.0107</v>
       </c>
     </row>
     <row r="12">
@@ -2921,22 +2921,22 @@
         <v>112</v>
       </c>
       <c r="B12" t="n">
-        <v>2.81</v>
+        <v>2.51</v>
       </c>
       <c r="C12" t="n">
-        <v>2.553</v>
+        <v>2.204</v>
       </c>
       <c r="D12" s="1" t="n">
-        <v>42767</v>
+        <v>42736</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.257</v>
+        <v>-0.306</v>
       </c>
       <c r="F12" t="n">
-        <v>0.257</v>
+        <v>0.306</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0662</v>
+        <v>0.0938</v>
       </c>
     </row>
     <row r="13">
@@ -2944,22 +2944,22 @@
         <v>113</v>
       </c>
       <c r="B13" t="n">
-        <v>2.441</v>
+        <v>2.81</v>
       </c>
       <c r="C13" t="n">
-        <v>2.764</v>
+        <v>2.556</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>42795</v>
+        <v>42767</v>
       </c>
       <c r="E13" t="n">
-        <v>0.323</v>
+        <v>-0.254</v>
       </c>
       <c r="F13" t="n">
-        <v>0.323</v>
+        <v>0.254</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1043</v>
+        <v>0.0648</v>
       </c>
     </row>
     <row r="14">
@@ -2967,22 +2967,22 @@
         <v>114</v>
       </c>
       <c r="B14" t="n">
-        <v>2.176</v>
+        <v>2.441</v>
       </c>
       <c r="C14" t="n">
-        <v>2.691</v>
+        <v>2.761</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>42826</v>
+        <v>42795</v>
       </c>
       <c r="E14" t="n">
-        <v>0.515</v>
+        <v>0.32</v>
       </c>
       <c r="F14" t="n">
-        <v>0.515</v>
+        <v>0.32</v>
       </c>
       <c r="G14" t="n">
-        <v>0.2648</v>
+        <v>0.1022</v>
       </c>
     </row>
     <row r="15">
@@ -2990,22 +2990,22 @@
         <v>115</v>
       </c>
       <c r="B15" t="n">
-        <v>1.856</v>
+        <v>2.176</v>
       </c>
       <c r="C15" t="n">
-        <v>2.162</v>
+        <v>2.684</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>42856</v>
+        <v>42826</v>
       </c>
       <c r="E15" t="n">
-        <v>0.306</v>
+        <v>0.508</v>
       </c>
       <c r="F15" t="n">
-        <v>0.306</v>
+        <v>0.508</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0934</v>
+        <v>0.2578</v>
       </c>
     </row>
     <row r="16">
@@ -3013,22 +3013,22 @@
         <v>116</v>
       </c>
       <c r="B16" t="n">
-        <v>1.641</v>
+        <v>1.856</v>
       </c>
       <c r="C16" t="n">
-        <v>1.745</v>
+        <v>2.129</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>42887</v>
+        <v>42856</v>
       </c>
       <c r="E16" t="n">
-        <v>0.104</v>
+        <v>0.273</v>
       </c>
       <c r="F16" t="n">
-        <v>0.104</v>
+        <v>0.273</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0108</v>
+        <v>0.0745</v>
       </c>
     </row>
     <row r="17">
@@ -3036,22 +3036,22 @@
         <v>117</v>
       </c>
       <c r="B17" t="n">
-        <v>1.725</v>
+        <v>1.641</v>
       </c>
       <c r="C17" t="n">
-        <v>1.653</v>
+        <v>1.719</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>42917</v>
+        <v>42887</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.073</v>
+        <v>0.079</v>
       </c>
       <c r="F17" t="n">
-        <v>0.073</v>
+        <v>0.079</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0053</v>
+        <v>0.0062</v>
       </c>
     </row>
     <row r="18">
@@ -3059,22 +3059,22 @@
         <v>118</v>
       </c>
       <c r="B18" t="n">
-        <v>1.928</v>
+        <v>1.725</v>
       </c>
       <c r="C18" t="n">
-        <v>1.799</v>
+        <v>1.597</v>
       </c>
       <c r="D18" s="1" t="n">
-        <v>42948</v>
+        <v>42917</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.129</v>
+        <v>-0.128</v>
       </c>
       <c r="F18" t="n">
-        <v>0.129</v>
+        <v>0.128</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0167</v>
+        <v>0.0163</v>
       </c>
     </row>
     <row r="19">
@@ -3082,22 +3082,22 @@
         <v>119</v>
       </c>
       <c r="B19" t="n">
-        <v>2.181</v>
+        <v>1.928</v>
       </c>
       <c r="C19" t="n">
-        <v>2.057</v>
+        <v>1.786</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>42979</v>
+        <v>42948</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.124</v>
+        <v>-0.142</v>
       </c>
       <c r="F19" t="n">
-        <v>0.124</v>
+        <v>0.142</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0153</v>
+        <v>0.0202</v>
       </c>
     </row>
     <row r="20">
@@ -3105,22 +3105,22 @@
         <v>120</v>
       </c>
       <c r="B20" t="n">
-        <v>2.021</v>
+        <v>2.181</v>
       </c>
       <c r="C20" t="n">
-        <v>2.214</v>
+        <v>2.018</v>
       </c>
       <c r="D20" s="1" t="n">
-        <v>43009</v>
+        <v>42979</v>
       </c>
       <c r="E20" t="n">
-        <v>0.193</v>
+        <v>-0.162</v>
       </c>
       <c r="F20" t="n">
-        <v>0.193</v>
+        <v>0.162</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0373</v>
+        <v>0.0264</v>
       </c>
     </row>
     <row r="21">
@@ -3128,22 +3128,22 @@
         <v>121</v>
       </c>
       <c r="B21" t="n">
-        <v>2.172</v>
+        <v>2.021</v>
       </c>
       <c r="C21" t="n">
-        <v>2.057</v>
+        <v>2.182</v>
       </c>
       <c r="D21" s="1" t="n">
-        <v>43040</v>
+        <v>43009</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.116</v>
+        <v>0.161</v>
       </c>
       <c r="F21" t="n">
-        <v>0.116</v>
+        <v>0.161</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0134</v>
+        <v>0.0259</v>
       </c>
     </row>
     <row r="22">
@@ -3151,22 +3151,22 @@
         <v>122</v>
       </c>
       <c r="B22" t="n">
-        <v>2.13</v>
+        <v>2.172</v>
       </c>
       <c r="C22" t="n">
-        <v>2.156</v>
+        <v>2.018</v>
       </c>
       <c r="D22" s="1" t="n">
-        <v>43070</v>
+        <v>43040</v>
       </c>
       <c r="E22" t="n">
-        <v>0.026</v>
+        <v>-0.154</v>
       </c>
       <c r="F22" t="n">
-        <v>0.026</v>
+        <v>0.154</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0007</v>
+        <v>0.0238</v>
       </c>
     </row>
     <row r="23">
@@ -3174,22 +3174,22 @@
         <v>123</v>
       </c>
       <c r="B23" t="n">
-        <v>2.151</v>
+        <v>2.13</v>
       </c>
       <c r="C23" t="n">
-        <v>2.367</v>
+        <v>2.096</v>
       </c>
       <c r="D23" s="1" t="n">
-        <v>43101</v>
+        <v>43070</v>
       </c>
       <c r="E23" t="n">
-        <v>0.215</v>
+        <v>-0.034</v>
       </c>
       <c r="F23" t="n">
-        <v>0.215</v>
+        <v>0.034</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0463</v>
+        <v>0.0012</v>
       </c>
     </row>
     <row r="24">
@@ -3197,22 +3197,22 @@
         <v>124</v>
       </c>
       <c r="B24" t="n">
-        <v>2.263</v>
+        <v>2.151</v>
       </c>
       <c r="C24" t="n">
-        <v>2.326</v>
+        <v>2.337</v>
       </c>
       <c r="D24" s="1" t="n">
-        <v>43132</v>
+        <v>43101</v>
       </c>
       <c r="E24" t="n">
-        <v>0.063</v>
+        <v>0.185</v>
       </c>
       <c r="F24" t="n">
-        <v>0.063</v>
+        <v>0.185</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0039</v>
+        <v>0.0344</v>
       </c>
     </row>
     <row r="25">
@@ -3220,22 +3220,22 @@
         <v>125</v>
       </c>
       <c r="B25" t="n">
-        <v>2.331</v>
+        <v>2.263</v>
       </c>
       <c r="C25" t="n">
-        <v>2.219</v>
+        <v>2.311</v>
       </c>
       <c r="D25" s="1" t="n">
-        <v>43160</v>
+        <v>43132</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.112</v>
+        <v>0.047</v>
       </c>
       <c r="F25" t="n">
-        <v>0.112</v>
+        <v>0.047</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0125</v>
+        <v>0.0022</v>
       </c>
     </row>
     <row r="26">
@@ -3243,22 +3243,22 @@
         <v>126</v>
       </c>
       <c r="B26" t="n">
-        <v>2.471</v>
+        <v>2.331</v>
       </c>
       <c r="C26" t="n">
-        <v>2.489</v>
+        <v>2.208</v>
       </c>
       <c r="D26" s="1" t="n">
-        <v>43191</v>
+        <v>43160</v>
       </c>
       <c r="E26" t="n">
-        <v>0.018</v>
+        <v>-0.123</v>
       </c>
       <c r="F26" t="n">
-        <v>0.018</v>
+        <v>0.123</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0003</v>
+        <v>0.0151</v>
       </c>
     </row>
     <row r="27">
@@ -3266,22 +3266,22 @@
         <v>127</v>
       </c>
       <c r="B27" t="n">
-        <v>2.782</v>
+        <v>2.471</v>
       </c>
       <c r="C27" t="n">
-        <v>2.559</v>
+        <v>2.5</v>
       </c>
       <c r="D27" s="1" t="n">
-        <v>43221</v>
+        <v>43191</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.223</v>
+        <v>0.029</v>
       </c>
       <c r="F27" t="n">
-        <v>0.223</v>
+        <v>0.029</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0497</v>
+        <v>0.0009</v>
       </c>
     </row>
     <row r="28">
@@ -3289,22 +3289,22 @@
         <v>128</v>
       </c>
       <c r="B28" t="n">
-        <v>2.808</v>
+        <v>2.782</v>
       </c>
       <c r="C28" t="n">
-        <v>2.834</v>
+        <v>2.576</v>
       </c>
       <c r="D28" s="1" t="n">
-        <v>43252</v>
+        <v>43221</v>
       </c>
       <c r="E28" t="n">
-        <v>0.026</v>
+        <v>-0.206</v>
       </c>
       <c r="F28" t="n">
-        <v>0.026</v>
+        <v>0.206</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0007</v>
+        <v>0.0424</v>
       </c>
     </row>
     <row r="29">
@@ -3312,22 +3312,22 @@
         <v>129</v>
       </c>
       <c r="B29" t="n">
-        <v>2.854</v>
+        <v>2.808</v>
       </c>
       <c r="C29" t="n">
-        <v>2.737</v>
+        <v>2.821</v>
       </c>
       <c r="D29" s="1" t="n">
-        <v>43282</v>
+        <v>43252</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.118</v>
+        <v>0.013</v>
       </c>
       <c r="F29" t="n">
-        <v>0.118</v>
+        <v>0.013</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0138</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="30">
@@ -3335,22 +3335,22 @@
         <v>130</v>
       </c>
       <c r="B30" t="n">
-        <v>2.643</v>
+        <v>2.854</v>
       </c>
       <c r="C30" t="n">
-        <v>2.757</v>
+        <v>2.731</v>
       </c>
       <c r="D30" s="1" t="n">
-        <v>43313</v>
+        <v>43282</v>
       </c>
       <c r="E30" t="n">
-        <v>0.114</v>
+        <v>-0.123</v>
       </c>
       <c r="F30" t="n">
-        <v>0.114</v>
+        <v>0.123</v>
       </c>
       <c r="G30" t="n">
-        <v>0.013</v>
+        <v>0.0151</v>
       </c>
     </row>
     <row r="31">
@@ -3358,22 +3358,22 @@
         <v>131</v>
       </c>
       <c r="B31" t="n">
-        <v>2.332</v>
+        <v>2.643</v>
       </c>
       <c r="C31" t="n">
-        <v>2.617</v>
+        <v>2.752</v>
       </c>
       <c r="D31" s="1" t="n">
-        <v>43344</v>
+        <v>43313</v>
       </c>
       <c r="E31" t="n">
-        <v>0.285</v>
+        <v>0.109</v>
       </c>
       <c r="F31" t="n">
-        <v>0.285</v>
+        <v>0.109</v>
       </c>
       <c r="G31" t="n">
-        <v>0.0813</v>
+        <v>0.0119</v>
       </c>
     </row>
     <row r="32">
@@ -3381,22 +3381,22 @@
         <v>132</v>
       </c>
       <c r="B32" t="n">
-        <v>2.492</v>
+        <v>2.332</v>
       </c>
       <c r="C32" t="n">
-        <v>2.413</v>
+        <v>2.627</v>
       </c>
       <c r="D32" s="1" t="n">
-        <v>43374</v>
+        <v>43344</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.079</v>
+        <v>0.295</v>
       </c>
       <c r="F32" t="n">
-        <v>0.079</v>
+        <v>0.295</v>
       </c>
       <c r="G32" t="n">
-        <v>0.0062</v>
+        <v>0.087</v>
       </c>
     </row>
     <row r="33">
@@ -3404,22 +3404,22 @@
         <v>133</v>
       </c>
       <c r="B33" t="n">
-        <v>2.147</v>
+        <v>2.492</v>
       </c>
       <c r="C33" t="n">
-        <v>2.316</v>
+        <v>2.387</v>
       </c>
       <c r="D33" s="1" t="n">
-        <v>43405</v>
+        <v>43374</v>
       </c>
       <c r="E33" t="n">
-        <v>0.168</v>
+        <v>-0.105</v>
       </c>
       <c r="F33" t="n">
-        <v>0.168</v>
+        <v>0.105</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0284</v>
+        <v>0.0111</v>
       </c>
     </row>
     <row r="34">
@@ -3427,22 +3427,22 @@
         <v>134</v>
       </c>
       <c r="B34" t="n">
-        <v>2.002</v>
+        <v>2.147</v>
       </c>
       <c r="C34" t="n">
-        <v>2.149</v>
+        <v>2.302</v>
       </c>
       <c r="D34" s="1" t="n">
-        <v>43435</v>
+        <v>43405</v>
       </c>
       <c r="E34" t="n">
-        <v>0.147</v>
+        <v>0.154</v>
       </c>
       <c r="F34" t="n">
-        <v>0.147</v>
+        <v>0.154</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0216</v>
+        <v>0.0238</v>
       </c>
     </row>
     <row r="35">
@@ -3450,22 +3450,22 @@
         <v>135</v>
       </c>
       <c r="B35" t="n">
-        <v>1.488</v>
+        <v>2.002</v>
       </c>
       <c r="C35" t="n">
-        <v>1.878</v>
+        <v>2.115</v>
       </c>
       <c r="D35" s="1" t="n">
-        <v>43466</v>
+        <v>43435</v>
       </c>
       <c r="E35" t="n">
-        <v>0.391</v>
+        <v>0.113</v>
       </c>
       <c r="F35" t="n">
-        <v>0.391</v>
+        <v>0.113</v>
       </c>
       <c r="G35" t="n">
-        <v>0.1527</v>
+        <v>0.0127</v>
       </c>
     </row>
     <row r="36">
@@ -3473,22 +3473,22 @@
         <v>136</v>
       </c>
       <c r="B36" t="n">
-        <v>1.519</v>
+        <v>1.488</v>
       </c>
       <c r="C36" t="n">
-        <v>1.598</v>
+        <v>1.801</v>
       </c>
       <c r="D36" s="1" t="n">
-        <v>43497</v>
+        <v>43466</v>
       </c>
       <c r="E36" t="n">
-        <v>0.08</v>
+        <v>0.314</v>
       </c>
       <c r="F36" t="n">
-        <v>0.08</v>
+        <v>0.314</v>
       </c>
       <c r="G36" t="n">
-        <v>0.0063</v>
+        <v>0.0984</v>
       </c>
     </row>
     <row r="37">
@@ -3496,22 +3496,22 @@
         <v>137</v>
       </c>
       <c r="B37" t="n">
-        <v>1.883</v>
+        <v>1.519</v>
       </c>
       <c r="C37" t="n">
-        <v>1.733</v>
+        <v>1.625</v>
       </c>
       <c r="D37" s="1" t="n">
-        <v>43525</v>
+        <v>43497</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.15</v>
+        <v>0.106</v>
       </c>
       <c r="F37" t="n">
-        <v>0.15</v>
+        <v>0.106</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0224</v>
+        <v>0.0112</v>
       </c>
     </row>
     <row r="38">
@@ -3519,22 +3519,22 @@
         <v>138</v>
       </c>
       <c r="B38" t="n">
-        <v>2.001</v>
+        <v>1.883</v>
       </c>
       <c r="C38" t="n">
-        <v>1.849</v>
+        <v>1.787</v>
       </c>
       <c r="D38" s="1" t="n">
-        <v>43556</v>
+        <v>43525</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.151</v>
+        <v>-0.096</v>
       </c>
       <c r="F38" t="n">
-        <v>0.151</v>
+        <v>0.096</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0228</v>
+        <v>0.0092</v>
       </c>
     </row>
     <row r="39">
@@ -3542,22 +3542,22 @@
         <v>139</v>
       </c>
       <c r="B39" t="n">
-        <v>1.796</v>
+        <v>2.001</v>
       </c>
       <c r="C39" t="n">
-        <v>1.982</v>
+        <v>1.867</v>
       </c>
       <c r="D39" s="1" t="n">
-        <v>43586</v>
+        <v>43556</v>
       </c>
       <c r="E39" t="n">
-        <v>0.186</v>
+        <v>-0.133</v>
       </c>
       <c r="F39" t="n">
-        <v>0.186</v>
+        <v>0.133</v>
       </c>
       <c r="G39" t="n">
-        <v>0.0346</v>
+        <v>0.0177</v>
       </c>
     </row>
     <row r="40">
@@ -3565,22 +3565,22 @@
         <v>140</v>
       </c>
       <c r="B40" t="n">
-        <v>1.671</v>
+        <v>1.796</v>
       </c>
       <c r="C40" t="n">
-        <v>1.635</v>
+        <v>1.93</v>
       </c>
       <c r="D40" s="1" t="n">
-        <v>43617</v>
+        <v>43586</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.036</v>
+        <v>0.134</v>
       </c>
       <c r="F40" t="n">
-        <v>0.036</v>
+        <v>0.134</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0013</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="41">
@@ -3588,22 +3588,22 @@
         <v>141</v>
       </c>
       <c r="B41" t="n">
-        <v>1.826</v>
+        <v>1.671</v>
       </c>
       <c r="C41" t="n">
-        <v>1.784</v>
+        <v>1.645</v>
       </c>
       <c r="D41" s="1" t="n">
-        <v>43647</v>
+        <v>43617</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.043</v>
+        <v>-0.026</v>
       </c>
       <c r="F41" t="n">
-        <v>0.043</v>
+        <v>0.026</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0018</v>
+        <v>0.0007</v>
       </c>
     </row>
     <row r="42">
@@ -3611,22 +3611,22 @@
         <v>142</v>
       </c>
       <c r="B42" t="n">
-        <v>1.738</v>
+        <v>1.826</v>
       </c>
       <c r="C42" t="n">
-        <v>1.59</v>
+        <v>1.777</v>
       </c>
       <c r="D42" s="1" t="n">
-        <v>43678</v>
+        <v>43647</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.147</v>
+        <v>-0.05</v>
       </c>
       <c r="F42" t="n">
-        <v>0.147</v>
+        <v>0.05</v>
       </c>
       <c r="G42" t="n">
-        <v>0.0217</v>
+        <v>0.0025</v>
       </c>
     </row>
     <row r="43">
@@ -3634,22 +3634,22 @@
         <v>143</v>
       </c>
       <c r="B43" t="n">
-        <v>1.685</v>
+        <v>1.738</v>
       </c>
       <c r="C43" t="n">
-        <v>1.823</v>
+        <v>1.578</v>
       </c>
       <c r="D43" s="1" t="n">
-        <v>43709</v>
+        <v>43678</v>
       </c>
       <c r="E43" t="n">
-        <v>0.139</v>
+        <v>-0.159</v>
       </c>
       <c r="F43" t="n">
-        <v>0.139</v>
+        <v>0.159</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0193</v>
+        <v>0.0254</v>
       </c>
     </row>
     <row r="44">
@@ -3657,22 +3657,22 @@
         <v>144</v>
       </c>
       <c r="B44" t="n">
-        <v>1.734</v>
+        <v>1.685</v>
       </c>
       <c r="C44" t="n">
-        <v>1.796</v>
+        <v>1.813</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>43739</v>
+        <v>43709</v>
       </c>
       <c r="E44" t="n">
-        <v>0.062</v>
+        <v>0.128</v>
       </c>
       <c r="F44" t="n">
-        <v>0.062</v>
+        <v>0.128</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0039</v>
+        <v>0.0164</v>
       </c>
     </row>
     <row r="45">
@@ -3680,22 +3680,22 @@
         <v>145</v>
       </c>
       <c r="B45" t="n">
-        <v>2.092</v>
+        <v>1.734</v>
       </c>
       <c r="C45" t="n">
-        <v>1.799</v>
+        <v>1.817</v>
       </c>
       <c r="D45" s="1" t="n">
-        <v>43770</v>
+        <v>43739</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.294</v>
+        <v>0.083</v>
       </c>
       <c r="F45" t="n">
-        <v>0.294</v>
+        <v>0.083</v>
       </c>
       <c r="G45" t="n">
-        <v>0.0862</v>
+        <v>0.0069</v>
       </c>
     </row>
     <row r="46">
@@ -3703,22 +3703,22 @@
         <v>146</v>
       </c>
       <c r="B46" t="n">
-        <v>2.32</v>
+        <v>2.092</v>
       </c>
       <c r="C46" t="n">
-        <v>2.036</v>
+        <v>1.755</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>43800</v>
+        <v>43770</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.284</v>
+        <v>-0.337</v>
       </c>
       <c r="F46" t="n">
-        <v>0.284</v>
+        <v>0.337</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0804</v>
+        <v>0.1137</v>
       </c>
     </row>
     <row r="47">
@@ -3726,22 +3726,22 @@
         <v>147</v>
       </c>
       <c r="B47" t="n">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="C47" t="n">
-        <v>2.312</v>
+        <v>2.003</v>
       </c>
       <c r="D47" s="1" t="n">
-        <v>43831</v>
+        <v>43800</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.288</v>
+        <v>-0.317</v>
       </c>
       <c r="F47" t="n">
-        <v>0.288</v>
+        <v>0.317</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0827</v>
+        <v>0.1002</v>
       </c>
     </row>
     <row r="48">
@@ -3749,22 +3749,22 @@
         <v>148</v>
       </c>
       <c r="B48" t="n">
-        <v>2.341</v>
+        <v>2.6</v>
       </c>
       <c r="C48" t="n">
-        <v>2.505</v>
+        <v>2.303</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>43862</v>
+        <v>43831</v>
       </c>
       <c r="E48" t="n">
-        <v>0.163</v>
+        <v>-0.297</v>
       </c>
       <c r="F48" t="n">
-        <v>0.163</v>
+        <v>0.297</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0267</v>
+        <v>0.0881</v>
       </c>
     </row>
     <row r="49">
@@ -3772,22 +3772,22 @@
         <v>149</v>
       </c>
       <c r="B49" t="n">
-        <v>1.494</v>
+        <v>2.341</v>
       </c>
       <c r="C49" t="n">
-        <v>1.878</v>
+        <v>2.488</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>43891</v>
+        <v>43862</v>
       </c>
       <c r="E49" t="n">
-        <v>0.384</v>
+        <v>0.146</v>
       </c>
       <c r="F49" t="n">
-        <v>0.384</v>
+        <v>0.146</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1477</v>
+        <v>0.0214</v>
       </c>
     </row>
     <row r="50">
@@ -3795,22 +3795,22 @@
         <v>150</v>
       </c>
       <c r="B50" t="n">
-        <v>0.313</v>
+        <v>1.494</v>
       </c>
       <c r="C50" t="n">
-        <v>1.15</v>
+        <v>1.957</v>
       </c>
       <c r="D50" s="1" t="n">
-        <v>43922</v>
+        <v>43891</v>
       </c>
       <c r="E50" t="n">
-        <v>0.837</v>
+        <v>0.463</v>
       </c>
       <c r="F50" t="n">
-        <v>0.837</v>
+        <v>0.463</v>
       </c>
       <c r="G50" t="n">
-        <v>0.7003</v>
+        <v>0.2145</v>
       </c>
     </row>
     <row r="51">
@@ -3818,22 +3818,22 @@
         <v>151</v>
       </c>
       <c r="B51" t="n">
-        <v>0.198</v>
+        <v>0.313</v>
       </c>
       <c r="C51" t="n">
-        <v>0.258</v>
+        <v>1.268</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>43952</v>
+        <v>43922</v>
       </c>
       <c r="E51" t="n">
-        <v>0.06</v>
+        <v>0.955</v>
       </c>
       <c r="F51" t="n">
-        <v>0.06</v>
+        <v>0.955</v>
       </c>
       <c r="G51" t="n">
-        <v>0.0036</v>
+        <v>0.9119</v>
       </c>
     </row>
     <row r="52">
@@ -3841,22 +3841,22 @@
         <v>152</v>
       </c>
       <c r="B52" t="n">
-        <v>0.717</v>
+        <v>0.198</v>
       </c>
       <c r="C52" t="n">
-        <v>0.496</v>
+        <v>0.265</v>
       </c>
       <c r="D52" s="1" t="n">
-        <v>43983</v>
+        <v>43952</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.221</v>
+        <v>0.067</v>
       </c>
       <c r="F52" t="n">
-        <v>0.221</v>
+        <v>0.067</v>
       </c>
       <c r="G52" t="n">
-        <v>0.0488</v>
+        <v>0.0044</v>
       </c>
     </row>
     <row r="53">
@@ -3864,22 +3864,22 @@
         <v>153</v>
       </c>
       <c r="B53" t="n">
-        <v>0.997</v>
+        <v>0.717</v>
       </c>
       <c r="C53" t="n">
-        <v>0.851</v>
+        <v>0.492</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44013</v>
+        <v>43983</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.146</v>
+        <v>-0.225</v>
       </c>
       <c r="F53" t="n">
-        <v>0.146</v>
+        <v>0.225</v>
       </c>
       <c r="G53" t="n">
-        <v>0.0212</v>
+        <v>0.0504</v>
       </c>
     </row>
     <row r="54">
@@ -3887,22 +3887,22 @@
         <v>154</v>
       </c>
       <c r="B54" t="n">
-        <v>1.281</v>
+        <v>0.997</v>
       </c>
       <c r="C54" t="n">
-        <v>1.113</v>
+        <v>0.902</v>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44044</v>
+        <v>44013</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.168</v>
+        <v>-0.095</v>
       </c>
       <c r="F54" t="n">
-        <v>0.168</v>
+        <v>0.095</v>
       </c>
       <c r="G54" t="n">
-        <v>0.0282</v>
+        <v>0.0089</v>
       </c>
     </row>
     <row r="55">
@@ -3910,22 +3910,22 @@
         <v>155</v>
       </c>
       <c r="B55" t="n">
-        <v>1.391</v>
+        <v>1.281</v>
       </c>
       <c r="C55" t="n">
-        <v>1.329</v>
+        <v>1.098</v>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44075</v>
+        <v>44044</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.062</v>
+        <v>-0.183</v>
       </c>
       <c r="F55" t="n">
-        <v>0.062</v>
+        <v>0.183</v>
       </c>
       <c r="G55" t="n">
-        <v>0.0038</v>
+        <v>0.0335</v>
       </c>
     </row>
     <row r="56">
@@ -3933,22 +3933,22 @@
         <v>156</v>
       </c>
       <c r="B56" t="n">
-        <v>1.23</v>
+        <v>1.391</v>
       </c>
       <c r="C56" t="n">
-        <v>1.685</v>
+        <v>1.34</v>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44105</v>
+        <v>44075</v>
       </c>
       <c r="E56" t="n">
-        <v>0.455</v>
+        <v>-0.051</v>
       </c>
       <c r="F56" t="n">
-        <v>0.455</v>
+        <v>0.051</v>
       </c>
       <c r="G56" t="n">
-        <v>0.2069</v>
+        <v>0.0026</v>
       </c>
     </row>
     <row r="57">
@@ -3956,22 +3956,22 @@
         <v>157</v>
       </c>
       <c r="B57" t="n">
-        <v>1.176</v>
+        <v>1.23</v>
       </c>
       <c r="C57" t="n">
-        <v>1.42</v>
+        <v>1.752</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44136</v>
+        <v>44105</v>
       </c>
       <c r="E57" t="n">
-        <v>0.244</v>
+        <v>0.521</v>
       </c>
       <c r="F57" t="n">
-        <v>0.244</v>
+        <v>0.521</v>
       </c>
       <c r="G57" t="n">
-        <v>0.0598</v>
+        <v>0.2719</v>
       </c>
     </row>
     <row r="58">
@@ -3979,22 +3979,22 @@
         <v>158</v>
       </c>
       <c r="B58" t="n">
-        <v>1.32</v>
+        <v>1.176</v>
       </c>
       <c r="C58" t="n">
-        <v>1.404</v>
+        <v>1.405</v>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44166</v>
+        <v>44136</v>
       </c>
       <c r="E58" t="n">
-        <v>0.084</v>
+        <v>0.229</v>
       </c>
       <c r="F58" t="n">
-        <v>0.084</v>
+        <v>0.229</v>
       </c>
       <c r="G58" t="n">
-        <v>0.007</v>
+        <v>0.0526</v>
       </c>
     </row>
     <row r="59">
@@ -4002,22 +4002,22 @@
         <v>159</v>
       </c>
       <c r="B59" t="n">
-        <v>1.355</v>
+        <v>1.32</v>
       </c>
       <c r="C59" t="n">
-        <v>1.64</v>
+        <v>1.384</v>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44197</v>
+        <v>44166</v>
       </c>
       <c r="E59" t="n">
-        <v>0.285</v>
+        <v>0.063</v>
       </c>
       <c r="F59" t="n">
-        <v>0.285</v>
+        <v>0.063</v>
       </c>
       <c r="G59" t="n">
-        <v>0.0813</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="60">
@@ -4025,22 +4025,22 @@
         <v>160</v>
       </c>
       <c r="B60" t="n">
-        <v>1.668</v>
+        <v>1.355</v>
       </c>
       <c r="C60" t="n">
-        <v>1.549</v>
+        <v>1.558</v>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44228</v>
+        <v>44197</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.119</v>
+        <v>0.203</v>
       </c>
       <c r="F60" t="n">
-        <v>0.119</v>
+        <v>0.203</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0141</v>
+        <v>0.0412</v>
       </c>
     </row>
     <row r="61">
@@ -4048,22 +4048,22 @@
         <v>161</v>
       </c>
       <c r="B61" t="n">
-        <v>2.624</v>
+        <v>1.668</v>
       </c>
       <c r="C61" t="n">
-        <v>2.023</v>
+        <v>1.486</v>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44256</v>
+        <v>44228</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.601</v>
+        <v>-0.182</v>
       </c>
       <c r="F61" t="n">
-        <v>0.601</v>
+        <v>0.182</v>
       </c>
       <c r="G61" t="n">
-        <v>0.3613</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="62">
@@ -4071,22 +4071,22 @@
         <v>162</v>
       </c>
       <c r="B62" t="n">
-        <v>4.137</v>
+        <v>2.624</v>
       </c>
       <c r="C62" t="n">
-        <v>2.783</v>
+        <v>1.972</v>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44287</v>
+        <v>44256</v>
       </c>
       <c r="E62" t="n">
-        <v>-1.354</v>
+        <v>-0.652</v>
       </c>
       <c r="F62" t="n">
-        <v>1.354</v>
+        <v>0.652</v>
       </c>
       <c r="G62" t="n">
-        <v>1.833</v>
+        <v>0.4248</v>
       </c>
     </row>
     <row r="63">
@@ -4094,22 +4094,22 @@
         <v>163</v>
       </c>
       <c r="B63" t="n">
-        <v>4.926</v>
+        <v>4.137</v>
       </c>
       <c r="C63" t="n">
-        <v>4.047</v>
+        <v>2.783</v>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44317</v>
+        <v>44287</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.88</v>
+        <v>-1.355</v>
       </c>
       <c r="F63" t="n">
-        <v>0.88</v>
+        <v>1.355</v>
       </c>
       <c r="G63" t="n">
-        <v>0.7739</v>
+        <v>1.835</v>
       </c>
     </row>
     <row r="64">
@@ -4117,22 +4117,22 @@
         <v>164</v>
       </c>
       <c r="B64" t="n">
-        <v>5.317</v>
+        <v>4.926</v>
       </c>
       <c r="C64" t="n">
-        <v>3.991</v>
+        <v>4.136</v>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44348</v>
+        <v>44317</v>
       </c>
       <c r="E64" t="n">
-        <v>-1.327</v>
+        <v>-0.79</v>
       </c>
       <c r="F64" t="n">
-        <v>1.327</v>
+        <v>0.79</v>
       </c>
       <c r="G64" t="n">
-        <v>1.7604</v>
+        <v>0.6244</v>
       </c>
     </row>
     <row r="65">
@@ -4140,22 +4140,22 @@
         <v>165</v>
       </c>
       <c r="B65" t="n">
-        <v>5.269</v>
+        <v>5.317</v>
       </c>
       <c r="C65" t="n">
-        <v>3.964</v>
+        <v>4.078</v>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44378</v>
+        <v>44348</v>
       </c>
       <c r="E65" t="n">
-        <v>-1.305</v>
+        <v>-1.239</v>
       </c>
       <c r="F65" t="n">
-        <v>1.305</v>
+        <v>1.239</v>
       </c>
       <c r="G65" t="n">
-        <v>1.7022</v>
+        <v>1.5354</v>
       </c>
     </row>
     <row r="66">
@@ -4163,22 +4163,22 @@
         <v>166</v>
       </c>
       <c r="B66" t="n">
-        <v>5.181</v>
+        <v>5.269</v>
       </c>
       <c r="C66" t="n">
-        <v>3.933</v>
+        <v>4.048</v>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44409</v>
+        <v>44378</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.248</v>
+        <v>-1.221</v>
       </c>
       <c r="F66" t="n">
-        <v>1.248</v>
+        <v>1.221</v>
       </c>
       <c r="G66" t="n">
-        <v>1.5573</v>
+        <v>1.4918</v>
       </c>
     </row>
     <row r="67">
@@ -4186,22 +4186,22 @@
         <v>167</v>
       </c>
       <c r="B67" t="n">
-        <v>5.364</v>
+        <v>5.181</v>
       </c>
       <c r="C67" t="n">
-        <v>3.973</v>
+        <v>4.017</v>
       </c>
       <c r="D67" s="1" t="n">
-        <v>44440</v>
+        <v>44409</v>
       </c>
       <c r="E67" t="n">
-        <v>-1.391</v>
+        <v>-1.164</v>
       </c>
       <c r="F67" t="n">
-        <v>1.391</v>
+        <v>1.164</v>
       </c>
       <c r="G67" t="n">
-        <v>1.9345</v>
+        <v>1.3553</v>
       </c>
     </row>
     <row r="68">
@@ -4209,22 +4209,22 @@
         <v>168</v>
       </c>
       <c r="B68" t="n">
-        <v>6.227</v>
+        <v>5.364</v>
       </c>
       <c r="C68" t="n">
-        <v>4.08</v>
+        <v>4.021</v>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44470</v>
+        <v>44440</v>
       </c>
       <c r="E68" t="n">
-        <v>-2.146</v>
+        <v>-1.343</v>
       </c>
       <c r="F68" t="n">
-        <v>2.146</v>
+        <v>1.343</v>
       </c>
       <c r="G68" t="n">
-        <v>4.6064</v>
+        <v>1.8034</v>
       </c>
     </row>
     <row r="69">
@@ -4232,22 +4232,22 @@
         <v>169</v>
       </c>
       <c r="B69" t="n">
-        <v>6.866</v>
+        <v>6.227</v>
       </c>
       <c r="C69" t="n">
-        <v>3.991</v>
+        <v>4.087</v>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44501</v>
+        <v>44470</v>
       </c>
       <c r="E69" t="n">
-        <v>-2.875</v>
+        <v>-2.14</v>
       </c>
       <c r="F69" t="n">
-        <v>2.875</v>
+        <v>2.14</v>
       </c>
       <c r="G69" t="n">
-        <v>8.2653</v>
+        <v>4.5775</v>
       </c>
     </row>
     <row r="70">
@@ -4255,22 +4255,22 @@
         <v>170</v>
       </c>
       <c r="B70" t="n">
-        <v>7.159</v>
+        <v>6.866</v>
       </c>
       <c r="C70" t="n">
-        <v>3.753</v>
+        <v>4.074</v>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44531</v>
+        <v>44501</v>
       </c>
       <c r="E70" t="n">
-        <v>-3.407</v>
+        <v>-2.792</v>
       </c>
       <c r="F70" t="n">
-        <v>3.407</v>
+        <v>2.792</v>
       </c>
       <c r="G70" t="n">
-        <v>11.6052</v>
+        <v>7.7927</v>
       </c>
     </row>
     <row r="71">
@@ -4278,22 +4278,22 @@
         <v>171</v>
       </c>
       <c r="B71" t="n">
-        <v>7.578</v>
+        <v>7.159</v>
       </c>
       <c r="C71" t="n">
-        <v>4.08</v>
+        <v>3.771</v>
       </c>
       <c r="D71" s="1" t="n">
-        <v>44562</v>
+        <v>44531</v>
       </c>
       <c r="E71" t="n">
-        <v>-3.498</v>
+        <v>-3.388</v>
       </c>
       <c r="F71" t="n">
-        <v>3.498</v>
+        <v>3.388</v>
       </c>
       <c r="G71" t="n">
-        <v>12.2341</v>
+        <v>11.4816</v>
       </c>
     </row>
     <row r="72">
@@ -4301,22 +4301,22 @@
         <v>172</v>
       </c>
       <c r="B72" t="n">
-        <v>7.949</v>
+        <v>7.578</v>
       </c>
       <c r="C72" t="n">
-        <v>4.03</v>
+        <v>4.123</v>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44593</v>
+        <v>44562</v>
       </c>
       <c r="E72" t="n">
-        <v>-3.919</v>
+        <v>-3.455</v>
       </c>
       <c r="F72" t="n">
-        <v>3.919</v>
+        <v>3.455</v>
       </c>
       <c r="G72" t="n">
-        <v>15.3621</v>
+        <v>11.9383</v>
       </c>
     </row>
     <row r="73">
@@ -4324,22 +4324,22 @@
         <v>173</v>
       </c>
       <c r="B73" t="n">
-        <v>8.541</v>
+        <v>7.949</v>
       </c>
       <c r="C73" t="n">
-        <v>4.08</v>
+        <v>4.074</v>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44621</v>
+        <v>44593</v>
       </c>
       <c r="E73" t="n">
-        <v>-4.46</v>
+        <v>-3.875</v>
       </c>
       <c r="F73" t="n">
-        <v>4.46</v>
+        <v>3.875</v>
       </c>
       <c r="G73" t="n">
-        <v>19.8955</v>
+        <v>15.017</v>
       </c>
     </row>
     <row r="74">
@@ -4347,22 +4347,22 @@
         <v>174</v>
       </c>
       <c r="B74" t="n">
-        <v>8.235</v>
+        <v>8.541</v>
       </c>
       <c r="C74" t="n">
-        <v>4.014</v>
+        <v>4.123</v>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44652</v>
+        <v>44621</v>
       </c>
       <c r="E74" t="n">
-        <v>-4.222</v>
+        <v>-4.418</v>
       </c>
       <c r="F74" t="n">
-        <v>4.222</v>
+        <v>4.418</v>
       </c>
       <c r="G74" t="n">
-        <v>17.8221</v>
+        <v>19.5177</v>
       </c>
     </row>
     <row r="75">
@@ -4370,22 +4370,22 @@
         <v>175</v>
       </c>
       <c r="B75" t="n">
-        <v>8.53</v>
+        <v>8.235</v>
       </c>
       <c r="C75" t="n">
-        <v>4.05</v>
+        <v>4.04</v>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44682</v>
+        <v>44652</v>
       </c>
       <c r="E75" t="n">
-        <v>-4.48</v>
+        <v>-4.195</v>
       </c>
       <c r="F75" t="n">
-        <v>4.48</v>
+        <v>4.195</v>
       </c>
       <c r="G75" t="n">
-        <v>20.0688</v>
+        <v>17.6004</v>
       </c>
     </row>
     <row r="76">
@@ -4393,22 +4393,22 @@
         <v>176</v>
       </c>
       <c r="B76" t="n">
-        <v>8.999</v>
+        <v>8.53</v>
       </c>
       <c r="C76" t="n">
-        <v>4.05</v>
+        <v>4.114</v>
       </c>
       <c r="D76" s="1" t="n">
-        <v>44713</v>
+        <v>44682</v>
       </c>
       <c r="E76" t="n">
-        <v>-4.949</v>
+        <v>-4.416</v>
       </c>
       <c r="F76" t="n">
-        <v>4.949</v>
+        <v>4.416</v>
       </c>
       <c r="G76" t="n">
-        <v>24.4938</v>
+        <v>19.5005</v>
       </c>
     </row>
     <row r="77">
@@ -4416,22 +4416,22 @@
         <v>177</v>
       </c>
       <c r="B77" t="n">
-        <v>8.448</v>
+        <v>8.999</v>
       </c>
       <c r="C77" t="n">
-        <v>3.609</v>
+        <v>4.114</v>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44743</v>
+        <v>44713</v>
       </c>
       <c r="E77" t="n">
-        <v>-4.839</v>
+        <v>-4.885</v>
       </c>
       <c r="F77" t="n">
-        <v>4.839</v>
+        <v>4.885</v>
       </c>
       <c r="G77" t="n">
-        <v>23.4165</v>
+        <v>23.8651</v>
       </c>
     </row>
     <row r="78">
@@ -4439,22 +4439,22 @@
         <v>178</v>
       </c>
       <c r="B78" t="n">
-        <v>8.216</v>
+        <v>8.448</v>
       </c>
       <c r="C78" t="n">
-        <v>3.438</v>
+        <v>3.598</v>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44774</v>
+        <v>44743</v>
       </c>
       <c r="E78" t="n">
-        <v>-4.778</v>
+        <v>-4.849</v>
       </c>
       <c r="F78" t="n">
-        <v>4.778</v>
+        <v>4.849</v>
       </c>
       <c r="G78" t="n">
-        <v>22.8284</v>
+        <v>23.5156</v>
       </c>
     </row>
     <row r="79">
@@ -4462,22 +4462,22 @@
         <v>179</v>
       </c>
       <c r="B79" t="n">
-        <v>8.206</v>
+        <v>8.216</v>
       </c>
       <c r="C79" t="n">
-        <v>3.885</v>
+        <v>3.484</v>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44805</v>
+        <v>44774</v>
       </c>
       <c r="E79" t="n">
-        <v>-4.321</v>
+        <v>-4.733</v>
       </c>
       <c r="F79" t="n">
-        <v>4.321</v>
+        <v>4.733</v>
       </c>
       <c r="G79" t="n">
-        <v>18.668</v>
+        <v>22.3976</v>
       </c>
     </row>
     <row r="80">
@@ -4485,22 +4485,22 @@
         <v>180</v>
       </c>
       <c r="B80" t="n">
-        <v>7.757</v>
+        <v>8.206</v>
       </c>
       <c r="C80" t="n">
-        <v>3.622</v>
+        <v>3.869</v>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44835</v>
+        <v>44805</v>
       </c>
       <c r="E80" t="n">
-        <v>-4.135</v>
+        <v>-4.336</v>
       </c>
       <c r="F80" t="n">
-        <v>4.135</v>
+        <v>4.336</v>
       </c>
       <c r="G80" t="n">
-        <v>17.0964</v>
+        <v>18.8031</v>
       </c>
     </row>
     <row r="81">
@@ -4508,22 +4508,22 @@
         <v>181</v>
       </c>
       <c r="B81" t="n">
-        <v>7.131</v>
+        <v>7.757</v>
       </c>
       <c r="C81" t="n">
-        <v>3.841</v>
+        <v>3.614</v>
       </c>
       <c r="D81" s="1" t="n">
-        <v>44866</v>
+        <v>44835</v>
       </c>
       <c r="E81" t="n">
-        <v>-3.29</v>
+        <v>-4.144</v>
       </c>
       <c r="F81" t="n">
-        <v>3.29</v>
+        <v>4.144</v>
       </c>
       <c r="G81" t="n">
-        <v>10.826</v>
+        <v>17.1706</v>
       </c>
     </row>
     <row r="82">
@@ -4531,22 +4531,22 @@
         <v>182</v>
       </c>
       <c r="B82" t="n">
-        <v>6.411</v>
+        <v>7.131</v>
       </c>
       <c r="C82" t="n">
-        <v>3.539</v>
+        <v>3.771</v>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44896</v>
+        <v>44866</v>
       </c>
       <c r="E82" t="n">
-        <v>-2.872</v>
+        <v>-3.36</v>
       </c>
       <c r="F82" t="n">
-        <v>2.872</v>
+        <v>3.36</v>
       </c>
       <c r="G82" t="n">
-        <v>8.2463</v>
+        <v>11.2921</v>
       </c>
     </row>
     <row r="83">
@@ -4554,22 +4554,22 @@
         <v>183</v>
       </c>
       <c r="B83" t="n">
-        <v>6.34</v>
+        <v>6.411</v>
       </c>
       <c r="C83" t="n">
-        <v>3.875</v>
+        <v>3.529</v>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44927</v>
+        <v>44896</v>
       </c>
       <c r="E83" t="n">
-        <v>-2.466</v>
+        <v>-2.882</v>
       </c>
       <c r="F83" t="n">
-        <v>2.466</v>
+        <v>2.882</v>
       </c>
       <c r="G83" t="n">
-        <v>6.079</v>
+        <v>8.3075</v>
       </c>
     </row>
     <row r="84">
@@ -4577,22 +4577,22 @@
         <v>184</v>
       </c>
       <c r="B84" t="n">
-        <v>5.958</v>
+        <v>6.34</v>
       </c>
       <c r="C84" t="n">
-        <v>3.832</v>
+        <v>3.895</v>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44958</v>
+        <v>44927</v>
       </c>
       <c r="E84" t="n">
-        <v>-2.126</v>
+        <v>-2.445</v>
       </c>
       <c r="F84" t="n">
-        <v>2.126</v>
+        <v>2.445</v>
       </c>
       <c r="G84" t="n">
-        <v>4.5196</v>
+        <v>5.9799</v>
       </c>
     </row>
     <row r="85">
@@ -4600,22 +4600,22 @@
         <v>185</v>
       </c>
       <c r="B85" t="n">
-        <v>4.931</v>
+        <v>5.958</v>
       </c>
       <c r="C85" t="n">
-        <v>3.823</v>
+        <v>3.824</v>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44986</v>
+        <v>44958</v>
       </c>
       <c r="E85" t="n">
-        <v>-1.109</v>
+        <v>-2.134</v>
       </c>
       <c r="F85" t="n">
-        <v>1.109</v>
+        <v>2.134</v>
       </c>
       <c r="G85" t="n">
-        <v>1.229</v>
+        <v>4.5527</v>
       </c>
     </row>
     <row r="86">
@@ -4623,22 +4623,22 @@
         <v>186</v>
       </c>
       <c r="B86" t="n">
-        <v>4.947</v>
+        <v>4.931</v>
       </c>
       <c r="C86" t="n">
-        <v>3.775</v>
+        <v>3.815</v>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45017</v>
+        <v>44986</v>
       </c>
       <c r="E86" t="n">
-        <v>-1.172</v>
+        <v>-1.116</v>
       </c>
       <c r="F86" t="n">
-        <v>1.172</v>
+        <v>1.116</v>
       </c>
       <c r="G86" t="n">
-        <v>1.3733</v>
+        <v>1.2458</v>
       </c>
     </row>
     <row r="87">
@@ -4646,22 +4646,22 @@
         <v>187</v>
       </c>
       <c r="B87" t="n">
-        <v>4.125</v>
+        <v>4.947</v>
       </c>
       <c r="C87" t="n">
-        <v>3.648</v>
+        <v>3.766</v>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45047</v>
+        <v>45017</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.478</v>
+        <v>-1.181</v>
       </c>
       <c r="F87" t="n">
-        <v>0.478</v>
+        <v>1.181</v>
       </c>
       <c r="G87" t="n">
-        <v>0.2282</v>
+        <v>1.3944</v>
       </c>
     </row>
     <row r="88">
@@ -4669,22 +4669,22 @@
         <v>188</v>
       </c>
       <c r="B88" t="n">
-        <v>3.059</v>
+        <v>4.125</v>
       </c>
       <c r="C88" t="n">
-        <v>3.633</v>
+        <v>3.56</v>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45078</v>
+        <v>45047</v>
       </c>
       <c r="E88" t="n">
-        <v>0.574</v>
+        <v>-0.565</v>
       </c>
       <c r="F88" t="n">
-        <v>0.574</v>
+        <v>0.565</v>
       </c>
       <c r="G88" t="n">
-        <v>0.3296</v>
+        <v>0.3191</v>
       </c>
     </row>
     <row r="89">
@@ -4692,22 +4692,22 @@
         <v>189</v>
       </c>
       <c r="B89" t="n">
-        <v>3.28</v>
+        <v>3.059</v>
       </c>
       <c r="C89" t="n">
-        <v>3.134</v>
+        <v>3.71</v>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45108</v>
+        <v>45078</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.147</v>
+        <v>0.651</v>
       </c>
       <c r="F89" t="n">
-        <v>0.147</v>
+        <v>0.651</v>
       </c>
       <c r="G89" t="n">
-        <v>0.0215</v>
+        <v>0.4233</v>
       </c>
     </row>
     <row r="90">
@@ -4715,22 +4715,22 @@
         <v>190</v>
       </c>
       <c r="B90" t="n">
-        <v>3.719</v>
+        <v>3.28</v>
       </c>
       <c r="C90" t="n">
-        <v>3.142</v>
+        <v>3.113</v>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45139</v>
+        <v>45108</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.577</v>
+        <v>-0.168</v>
       </c>
       <c r="F90" t="n">
-        <v>0.577</v>
+        <v>0.168</v>
       </c>
       <c r="G90" t="n">
-        <v>0.3324</v>
+        <v>0.0281</v>
       </c>
     </row>
     <row r="91">
@@ -4738,22 +4738,22 @@
         <v>191</v>
       </c>
       <c r="B91" t="n">
-        <v>3.695</v>
+        <v>3.719</v>
       </c>
       <c r="C91" t="n">
-        <v>3.454</v>
+        <v>3.04</v>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45170</v>
+        <v>45139</v>
       </c>
       <c r="E91" t="n">
-        <v>-0.241</v>
+        <v>-0.679</v>
       </c>
       <c r="F91" t="n">
-        <v>0.241</v>
+        <v>0.679</v>
       </c>
       <c r="G91" t="n">
-        <v>0.058</v>
+        <v>0.4606</v>
       </c>
     </row>
     <row r="92">
@@ -4761,22 +4761,22 @@
         <v>192</v>
       </c>
       <c r="B92" t="n">
-        <v>3.247</v>
+        <v>3.695</v>
       </c>
       <c r="C92" t="n">
-        <v>3.145</v>
+        <v>3.499</v>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45200</v>
+        <v>45170</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.102</v>
+        <v>-0.197</v>
       </c>
       <c r="F92" t="n">
-        <v>0.102</v>
+        <v>0.197</v>
       </c>
       <c r="G92" t="n">
-        <v>0.0104</v>
+        <v>0.0386</v>
       </c>
     </row>
     <row r="93">
@@ -4784,22 +4784,22 @@
         <v>193</v>
       </c>
       <c r="B93" t="n">
-        <v>3.14</v>
+        <v>3.247</v>
       </c>
       <c r="C93" t="n">
-        <v>3.075</v>
+        <v>3.176</v>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45231</v>
+        <v>45200</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.065</v>
+        <v>-0.07</v>
       </c>
       <c r="F93" t="n">
-        <v>0.065</v>
+        <v>0.07</v>
       </c>
       <c r="G93" t="n">
-        <v>0.0042</v>
+        <v>0.0049</v>
       </c>
     </row>
     <row r="94">
@@ -4807,22 +4807,22 @@
         <v>194</v>
       </c>
       <c r="B94" t="n">
-        <v>3.322</v>
+        <v>3.14</v>
       </c>
       <c r="C94" t="n">
-        <v>2.942</v>
+        <v>3.055</v>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45261</v>
+        <v>45231</v>
       </c>
       <c r="E94" t="n">
-        <v>-0.381</v>
+        <v>-0.085</v>
       </c>
       <c r="F94" t="n">
-        <v>0.381</v>
+        <v>0.085</v>
       </c>
       <c r="G94" t="n">
-        <v>0.1448</v>
+        <v>0.0072</v>
       </c>
     </row>
     <row r="95">
@@ -4830,22 +4830,22 @@
         <v>195</v>
       </c>
       <c r="B95" t="n">
-        <v>3.108</v>
+        <v>3.322</v>
       </c>
       <c r="C95" t="n">
-        <v>3.341</v>
+        <v>2.927</v>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45292</v>
+        <v>45261</v>
       </c>
       <c r="E95" t="n">
-        <v>0.233</v>
+        <v>-0.395</v>
       </c>
       <c r="F95" t="n">
-        <v>0.233</v>
+        <v>0.395</v>
       </c>
       <c r="G95" t="n">
-        <v>0.0543</v>
+        <v>0.1559</v>
       </c>
     </row>
     <row r="96">
@@ -4853,22 +4853,22 @@
         <v>196</v>
       </c>
       <c r="B96" t="n">
-        <v>3.166</v>
+        <v>3.108</v>
       </c>
       <c r="C96" t="n">
-        <v>3.257</v>
+        <v>3.333</v>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45323</v>
+        <v>45292</v>
       </c>
       <c r="E96" t="n">
-        <v>0.09</v>
+        <v>0.225</v>
       </c>
       <c r="F96" t="n">
-        <v>0.09</v>
+        <v>0.225</v>
       </c>
       <c r="G96" t="n">
-        <v>0.0082</v>
+        <v>0.0507</v>
       </c>
     </row>
     <row r="97">
@@ -4876,22 +4876,22 @@
         <v>197</v>
       </c>
       <c r="B97" t="n">
-        <v>3.469</v>
+        <v>3.166</v>
       </c>
       <c r="C97" t="n">
-        <v>3.091</v>
+        <v>3.265</v>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45352</v>
+        <v>45323</v>
       </c>
       <c r="E97" t="n">
-        <v>-0.378</v>
+        <v>0.098</v>
       </c>
       <c r="F97" t="n">
-        <v>0.378</v>
+        <v>0.098</v>
       </c>
       <c r="G97" t="n">
-        <v>0.1433</v>
+        <v>0.0097</v>
       </c>
     </row>
     <row r="98">
@@ -4899,22 +4899,22 @@
         <v>198</v>
       </c>
       <c r="B98" t="n">
-        <v>3.354</v>
+        <v>3.469</v>
       </c>
       <c r="C98" t="n">
-        <v>3.335</v>
+        <v>3.076</v>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45383</v>
+        <v>45352</v>
       </c>
       <c r="E98" t="n">
-        <v>-0.019</v>
+        <v>-0.393</v>
       </c>
       <c r="F98" t="n">
-        <v>0.019</v>
+        <v>0.393</v>
       </c>
       <c r="G98" t="n">
-        <v>0.0004</v>
+        <v>0.1545</v>
       </c>
     </row>
     <row r="99">
@@ -4922,22 +4922,22 @@
         <v>199</v>
       </c>
       <c r="B99" t="n">
-        <v>3.239</v>
+        <v>3.354</v>
       </c>
       <c r="C99" t="n">
-        <v>3.15</v>
+        <v>3.363</v>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45413</v>
+        <v>45383</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.089</v>
+        <v>0.009</v>
       </c>
       <c r="F99" t="n">
-        <v>0.089</v>
+        <v>0.009</v>
       </c>
       <c r="G99" t="n">
-        <v>0.0079</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="100">
@@ -4945,22 +4945,22 @@
         <v>200</v>
       </c>
       <c r="B100" t="n">
-        <v>2.97</v>
+        <v>3.239</v>
       </c>
       <c r="C100" t="n">
-        <v>3.176</v>
+        <v>3.128</v>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45444</v>
+        <v>45413</v>
       </c>
       <c r="E100" t="n">
-        <v>0.206</v>
+        <v>-0.111</v>
       </c>
       <c r="F100" t="n">
-        <v>0.206</v>
+        <v>0.111</v>
       </c>
       <c r="G100" t="n">
-        <v>0.0422</v>
+        <v>0.0123</v>
       </c>
     </row>
     <row r="101">
@@ -4968,22 +4968,22 @@
         <v>201</v>
       </c>
       <c r="B101" t="n">
-        <v>2.938</v>
+        <v>2.97</v>
       </c>
       <c r="C101" t="n">
-        <v>2.83</v>
+        <v>3.177</v>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45474</v>
+        <v>45444</v>
       </c>
       <c r="E101" t="n">
-        <v>-0.109</v>
+        <v>0.207</v>
       </c>
       <c r="F101" t="n">
-        <v>0.109</v>
+        <v>0.207</v>
       </c>
       <c r="G101" t="n">
-        <v>0.0119</v>
+        <v>0.0428</v>
       </c>
     </row>
     <row r="102">
@@ -4991,22 +4991,22 @@
         <v>202</v>
       </c>
       <c r="B102" t="n">
-        <v>2.611</v>
+        <v>2.938</v>
       </c>
       <c r="C102" t="n">
-        <v>2.646</v>
+        <v>2.836</v>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45505</v>
+        <v>45474</v>
       </c>
       <c r="E102" t="n">
-        <v>0.035</v>
+        <v>-0.103</v>
       </c>
       <c r="F102" t="n">
-        <v>0.035</v>
+        <v>0.103</v>
       </c>
       <c r="G102" t="n">
-        <v>0.0012</v>
+        <v>0.0106</v>
       </c>
     </row>
     <row r="103">
@@ -5014,22 +5014,22 @@
         <v>203</v>
       </c>
       <c r="B103" t="n">
-        <v>2.433</v>
+        <v>2.611</v>
       </c>
       <c r="C103" t="n">
-        <v>2.423</v>
+        <v>2.641</v>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45536</v>
+        <v>45505</v>
       </c>
       <c r="E103" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="F103" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="G103" t="n">
-        <v>0.0001</v>
+        <v>0.0009</v>
       </c>
     </row>
     <row r="104">
@@ -5037,22 +5037,22 @@
         <v>204</v>
       </c>
       <c r="B104" t="n">
-        <v>2.571</v>
+        <v>2.433</v>
       </c>
       <c r="C104" t="n">
-        <v>2.527</v>
+        <v>2.407</v>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45566</v>
+        <v>45536</v>
       </c>
       <c r="E104" t="n">
-        <v>-0.044</v>
+        <v>-0.026</v>
       </c>
       <c r="F104" t="n">
-        <v>0.044</v>
+        <v>0.026</v>
       </c>
       <c r="G104" t="n">
-        <v>0.0019</v>
+        <v>0.0007</v>
       </c>
     </row>
     <row r="105">
@@ -5060,22 +5060,22 @@
         <v>205</v>
       </c>
       <c r="B105" t="n">
-        <v>2.714</v>
+        <v>2.571</v>
       </c>
       <c r="C105" t="n">
-        <v>2.522</v>
+        <v>2.514</v>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45597</v>
+        <v>45566</v>
       </c>
       <c r="E105" t="n">
-        <v>-0.192</v>
+        <v>-0.057</v>
       </c>
       <c r="F105" t="n">
-        <v>0.192</v>
+        <v>0.057</v>
       </c>
       <c r="G105" t="n">
-        <v>0.0369</v>
+        <v>0.0033</v>
       </c>
     </row>
     <row r="106">
@@ -5083,22 +5083,22 @@
         <v>206</v>
       </c>
       <c r="B106" t="n">
-        <v>2.872</v>
+        <v>2.714</v>
       </c>
       <c r="C106" t="n">
-        <v>2.406</v>
+        <v>2.469</v>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45627</v>
+        <v>45597</v>
       </c>
       <c r="E106" t="n">
-        <v>-0.467</v>
+        <v>-0.245</v>
       </c>
       <c r="F106" t="n">
-        <v>0.467</v>
+        <v>0.245</v>
       </c>
       <c r="G106" t="n">
-        <v>0.2177</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="107">
@@ -5106,22 +5106,22 @@
         <v>207</v>
       </c>
       <c r="B107" t="n">
-        <v>2.999</v>
+        <v>2.872</v>
       </c>
       <c r="C107" t="n">
-        <v>2.893</v>
+        <v>2.412</v>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45658</v>
+        <v>45627</v>
       </c>
       <c r="E107" t="n">
-        <v>-0.107</v>
+        <v>-0.46</v>
       </c>
       <c r="F107" t="n">
-        <v>0.107</v>
+        <v>0.46</v>
       </c>
       <c r="G107" t="n">
-        <v>0.0113</v>
+        <v>0.2118</v>
       </c>
     </row>
     <row r="108">
@@ -5129,22 +5129,22 @@
         <v>208</v>
       </c>
       <c r="B108" t="n">
-        <v>2.814</v>
+        <v>2.999</v>
       </c>
       <c r="C108" t="n">
-        <v>2.888</v>
+        <v>2.916</v>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45689</v>
+        <v>45658</v>
       </c>
       <c r="E108" t="n">
-        <v>0.074</v>
+        <v>-0.083</v>
       </c>
       <c r="F108" t="n">
-        <v>0.074</v>
+        <v>0.083</v>
       </c>
       <c r="G108" t="n">
-        <v>0.0055</v>
+        <v>0.0069</v>
       </c>
     </row>
     <row r="109">
@@ -5152,22 +5152,22 @@
         <v>209</v>
       </c>
       <c r="B109" t="n">
-        <v>2.406</v>
+        <v>2.814</v>
       </c>
       <c r="C109" t="n">
-        <v>2.66</v>
+        <v>2.927</v>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45717</v>
+        <v>45689</v>
       </c>
       <c r="E109" t="n">
-        <v>0.255</v>
+        <v>0.112</v>
       </c>
       <c r="F109" t="n">
-        <v>0.255</v>
+        <v>0.112</v>
       </c>
       <c r="G109" t="n">
-        <v>0.0649</v>
+        <v>0.0126</v>
       </c>
     </row>
     <row r="110">
@@ -5175,22 +5175,22 @@
         <v>210</v>
       </c>
       <c r="B110" t="n">
-        <v>2.334</v>
+        <v>2.406</v>
       </c>
       <c r="C110" t="n">
-        <v>2.301</v>
+        <v>2.714</v>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45748</v>
+        <v>45717</v>
       </c>
       <c r="E110" t="n">
-        <v>-0.033</v>
+        <v>0.308</v>
       </c>
       <c r="F110" t="n">
-        <v>0.033</v>
+        <v>0.308</v>
       </c>
       <c r="G110" t="n">
-        <v>0.0011</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="111">
@@ -5198,22 +5198,22 @@
         <v>211</v>
       </c>
       <c r="B111" t="n">
-        <v>2.376</v>
+        <v>2.334</v>
       </c>
       <c r="C111" t="n">
-        <v>2.346</v>
+        <v>2.289</v>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45778</v>
+        <v>45748</v>
       </c>
       <c r="E111" t="n">
-        <v>-0.03</v>
+        <v>-0.044</v>
       </c>
       <c r="F111" t="n">
-        <v>0.03</v>
+        <v>0.044</v>
       </c>
       <c r="G111" t="n">
-        <v>0.0009</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="112">
@@ -5221,22 +5221,22 @@
         <v>212</v>
       </c>
       <c r="B112" t="n">
-        <v>2.673</v>
+        <v>2.376</v>
       </c>
       <c r="C112" t="n">
-        <v>2.337</v>
+        <v>2.333</v>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45809</v>
+        <v>45778</v>
       </c>
       <c r="E112" t="n">
-        <v>-0.336</v>
+        <v>-0.043</v>
       </c>
       <c r="F112" t="n">
-        <v>0.336</v>
+        <v>0.043</v>
       </c>
       <c r="G112" t="n">
-        <v>0.1126</v>
+        <v>0.0019</v>
       </c>
     </row>
     <row r="113">
@@ -5244,22 +5244,22 @@
         <v>213</v>
       </c>
       <c r="B113" t="n">
-        <v>2.732</v>
+        <v>2.673</v>
       </c>
       <c r="C113" t="n">
-        <v>2.682</v>
+        <v>2.356</v>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45839</v>
+        <v>45809</v>
       </c>
       <c r="E113" t="n">
-        <v>-0.05</v>
+        <v>-0.317</v>
       </c>
       <c r="F113" t="n">
-        <v>0.05</v>
+        <v>0.317</v>
       </c>
       <c r="G113" t="n">
-        <v>0.0025</v>
+        <v>0.1006</v>
       </c>
     </row>
     <row r="114">
@@ -5267,22 +5267,22 @@
         <v>214</v>
       </c>
       <c r="B114" t="n">
-        <v>2.939</v>
+        <v>2.732</v>
       </c>
       <c r="C114" t="n">
-        <v>2.725</v>
+        <v>2.692</v>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45870</v>
+        <v>45839</v>
       </c>
       <c r="E114" t="n">
-        <v>-0.214</v>
+        <v>-0.04</v>
       </c>
       <c r="F114" t="n">
-        <v>0.214</v>
+        <v>0.04</v>
       </c>
       <c r="G114" t="n">
-        <v>0.0458</v>
+        <v>0.0016</v>
       </c>
     </row>
     <row r="115">
@@ -5290,22 +5290,22 @@
         <v>6</v>
       </c>
       <c r="B115" t="n">
-        <v>3.023</v>
+        <v>2.939</v>
       </c>
       <c r="C115" t="n">
-        <v>2.775</v>
+        <v>2.684</v>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45901</v>
+        <v>45870</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.247</v>
+        <v>-0.255</v>
       </c>
       <c r="F115" t="n">
-        <v>0.247</v>
+        <v>0.255</v>
       </c>
       <c r="G115" t="n">
-        <v>0.0612</v>
+        <v>0.0651</v>
       </c>
     </row>
   </sheetData>
